--- a/data/output/workbook/2026-07-09.xlsx
+++ b/data/output/workbook/2026-07-09.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09 12:05</t>
+          <t>2026-07-09 14:59</t>
         </is>
       </c>
     </row>
@@ -8836,13 +8836,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6295999999999999</v>
+        <v>0.6347</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8908,7 +8908,7 @@
         <v>-145</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-123</v>
+        <v>-116</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,32 +9081,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.2145</v>
+        <v>0.5528</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>366</v>
+        <v>-124</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 21.5% (fair +366). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Indiana Fever @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9162,14 +9162,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Over 171.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5665</v>
+        <v>0.582</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-131</v>
+        <v>-139</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>104</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9208,37 +9208,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo +6.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.2114</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-118</v>
+        <v>373</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 21.1% (fair +373). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9289,22 +9289,22 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +1.5</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5598000000000001</v>
+        <v>0.5639000000000001</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-127</v>
+        <v>-129</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9355,22 +9355,22 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Over 154.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.2357</v>
+        <v>0.5816</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>324</v>
+        <v>-139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>375</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 23.6% (fair +324). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9406,37 +9406,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 174.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.4796</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-120</v>
+        <v>109</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5333</v>
+        <v>0.5288</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9538,37 +9538,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Dallas Wings @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Toronto Tempo +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5445</v>
+        <v>0.5415</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9609,32 +9609,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Indiana Fever @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Indiana Fever +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5124</v>
+        <v>0.5598000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-105</v>
+        <v>-127</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9700,7 +9700,7 @@
         <v>-119</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9741,32 +9741,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5575</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,12 +9807,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9822,17 +9822,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3018</v>
+        <v>0.5541</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>231</v>
+        <v>-124</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>257</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9868,17 +9868,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4963</v>
+        <v>0.4894</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9934,37 +9934,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 180.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.5422</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>110</v>
+        <v>-118</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Dallas Wings @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.3018</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>117</v>
+        <v>257</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 30.2% (fair +231). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5057</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,12 +10137,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10152,17 +10152,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.2428</v>
+        <v>0.5009</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>312</v>
+        <v>-100</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>340</v>
+        <v>115</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 24.3% (fair +312). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,32 +10203,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 168.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4921</v>
+        <v>0.537</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>103</v>
+        <v>-116</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10269,32 +10269,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.4754</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-110</v>
+        <v>110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5277000000000001</v>
+        <v>0.5286</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-112</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10396,37 +10396,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5225</v>
+        <v>0.5119</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-109</v>
+        <v>-105</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10483,7 +10483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4775</v>
+        <v>0.4735</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,13 +10693,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5225</v>
+        <v>0.5265</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10831,7 +10831,7 @@
         <v>-145</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6186</v>
+        <v>0.6147</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-162</v>
+        <v>-160</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-144</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,13 +10957,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3814</v>
+        <v>0.3853</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,10 +11023,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4364</v>
+        <v>0.4353</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>127</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,13 +11089,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5636</v>
+        <v>0.5647</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11161,7 +11161,7 @@
         <v>119</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11227,7 +11227,7 @@
         <v>-119</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11419,13 +11419,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.419</v>
+        <v>0.4257</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,13 +11485,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.581</v>
+        <v>0.5743</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-139</v>
+        <v>-135</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11551,10 +11551,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.5201</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.4799</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,13 +11683,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4</v>
+        <v>0.3893</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,13 +11749,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6</v>
+        <v>0.6107</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-150</v>
+        <v>-157</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,13 +11815,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4575</v>
+        <v>0.4576</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>119</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11881,13 +11881,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5425</v>
+        <v>0.5424</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-119</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11943,17 +11943,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4335</v>
+        <v>0.4522</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12009,17 +12009,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5665</v>
+        <v>0.4658</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-131</v>
+        <v>115</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3662</v>
+        <v>0.3652</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>163</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6337999999999999</v>
+        <v>0.6348</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-170</v>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5037</v>
+        <v>0.4991</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-101</v>
+        <v>100</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,13 +12277,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4963</v>
+        <v>0.5009</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>101</v>
+        <v>-100</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12339,17 +12339,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4248</v>
+        <v>0.5151</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>135</v>
+        <v>-106</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>114</v>
+        <v>-104</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12405,17 +12405,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4886999999999999</v>
+        <v>0.4849</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12475,13 +12475,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6005</v>
+        <v>0.6111</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-150</v>
+        <v>-157</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3995</v>
+        <v>0.3889</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4494984</v>
+        <v>0.4831</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +122). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5505016</v>
+        <v>0.5169</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-122</v>
+        <v>-107</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -122). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12739,13 +12739,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4491</v>
+        <v>0.4472</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12805,13 +12805,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5528</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.3653</v>
       </c>
       <c r="G39" s="14" t="n">
+        <v>174</v>
+      </c>
+      <c r="H39" s="15" t="n">
         <v>170</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>175</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6295999999999999</v>
+        <v>0.6347</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4411</v>
+        <v>0.4477</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13069,13 +13069,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5589</v>
+        <v>0.5523</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-127</v>
+        <v>-123</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-121</v>
+        <v>-117</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13131,17 +13131,17 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5445</v>
+        <v>0.5361</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-120</v>
+        <v>-116</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13197,14 +13197,14 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.3699</v>
+        <v>0.4639</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>117</v>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,13 +13267,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3867</v>
+        <v>0.3838</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +159). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6133</v>
+        <v>0.6162000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-159</v>
+        <v>-161</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>-170</v>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -159). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13399,13 +13399,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5079</v>
+        <v>0.5038</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13465,13 +13465,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4921</v>
+        <v>0.4962</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5124</v>
+        <v>0.5288</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>113</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4876</v>
+        <v>0.4712</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>113</v>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6056</v>
+        <v>0.6057</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>-154</v>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3944</v>
+        <v>0.3943</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>154</v>
@@ -13927,13 +13927,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4289</v>
+        <v>0.4283</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>133</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.8% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,13 +13993,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4889999999999999</v>
+        <v>0.4897</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>104</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-107</v>
+        <v>-113</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4723</v>
+        <v>0.4714</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>112</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5277000000000001</v>
+        <v>0.5286</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-112</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14191,13 +14191,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.5246</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-110</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.4754</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>110</v>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14323,13 +14323,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4894</v>
+        <v>0.4901</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>104</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5105999999999999</v>
+        <v>0.5099</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>-104</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5788</v>
+        <v>0.5808</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-137</v>
+        <v>-139</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>-133</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,13 +14521,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4212</v>
+        <v>0.4192</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4765</v>
+        <v>0.4729</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5235</v>
+        <v>0.5271</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -15235,13 +15235,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.55</v>
+        <v>0.5204</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-122</v>
+        <v>-109</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 52.0% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15301,13 +15301,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.45</v>
+        <v>0.4796</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15348,32 +15348,32 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4139</v>
+        <v>0.4953</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>133</v>
+        <v>-113</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15397,7 +15397,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15414,32 +15414,32 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5861</v>
+        <v>0.5046999999999999</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-142</v>
+        <v>-102</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-133</v>
+        <v>102</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15480,32 +15480,32 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5105</v>
+        <v>0.5678</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-104</v>
+        <v>-131</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>104</v>
+        <v>-120</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15546,32 +15546,32 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4895</v>
+        <v>0.4322</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15612,12 +15612,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -15627,17 +15627,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4637</v>
+        <v>0.408</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15678,12 +15678,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -15693,17 +15693,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5363</v>
+        <v>0.592</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-116</v>
+        <v>-145</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-113</v>
+        <v>-138</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15744,32 +15744,32 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4762999999999999</v>
+        <v>0.4643</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15810,32 +15810,32 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5357000000000001</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15876,32 +15876,32 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4424</v>
+        <v>0.4266</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15942,32 +15942,32 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5576</v>
+        <v>0.5734</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-126</v>
+        <v>-134</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-122</v>
+        <v>-145</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16008,12 +16008,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4256172</v>
+        <v>0.5057</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>135</v>
+        <v>-102</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16074,12 +16074,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -16089,17 +16089,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5743828</v>
+        <v>0.4943</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-135</v>
+        <v>102</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>122</v>
+        <v>-105</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16140,32 +16140,32 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5069</v>
+        <v>0.5119</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-122</v>
+        <v>108</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16189,7 +16189,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16206,32 +16206,32 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.4881</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>117</v>
+        <v>-120</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16272,31 +16272,33 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.45</v>
+        <v>0.5775</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>122</v>
-      </c>
-      <c r="H91" s="15" t="n"/>
+        <v>-137</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>-167</v>
+      </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
         <v/>
@@ -16319,7 +16321,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16336,31 +16338,33 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.55</v>
+        <v>0.4225</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H92" s="15" t="n"/>
+        <v>137</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>150</v>
+      </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
         <v/>
@@ -16383,7 +16387,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16400,12 +16404,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -16415,16 +16419,18 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5083</v>
+        <v>0.474</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-103</v>
-      </c>
-      <c r="H93" s="15" t="n"/>
+        <v>111</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
         <v/>
@@ -16447,7 +16453,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16464,12 +16470,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -16479,16 +16485,18 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4917</v>
+        <v>0.526</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>103</v>
-      </c>
-      <c r="H94" s="15" t="n"/>
+        <v>-111</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-104</v>
+      </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
         <v/>
@@ -16511,7 +16519,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16528,31 +16536,33 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4815</v>
+        <v>0.4875</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="H95" s="15" t="n"/>
+        <v>105</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
         <v/>
@@ -16575,7 +16585,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16592,31 +16602,33 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5185</v>
+        <v>0.5125</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H96" s="15" t="n"/>
+        <v>-105</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
         <v/>
@@ -16639,7 +16651,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16656,31 +16668,33 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.3488</v>
+        <v>0.6283</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>187</v>
-      </c>
-      <c r="H97" s="15" t="n"/>
+        <v>-169</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>-188</v>
+      </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
         <v/>
@@ -16703,7 +16717,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +187). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16720,31 +16734,33 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.6512</v>
+        <v>0.3717</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-187</v>
-      </c>
-      <c r="H98" s="15" t="n"/>
+        <v>169</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>155</v>
+      </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
         <v/>
@@ -16767,7 +16783,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -187). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16784,12 +16800,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -16799,16 +16815,18 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.4699</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="H99" s="15" t="n"/>
+        <v>113</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
         <v/>
@@ -16831,7 +16849,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16848,12 +16866,12 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -16863,16 +16881,18 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5389</v>
+        <v>0.5301</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H100" s="15" t="n"/>
+        <v>-113</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
         <v/>
@@ -16895,7 +16915,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16904,9 +16924,1835 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.9% (fair +123). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>-123</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.1% (fair -123). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Over 7.5</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I103" s="13">
+        <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="16">
+        <f>IF($H$103="","",$F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF($H$103="","",MAX(0,($F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))/IF($H$103&lt;0,-100/$H$103,$H$103/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>IF($H$103="","",ROUND(MIN($K$103,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M103" s="12">
+        <f>IF($J$103="","",IF($J$103&lt;0,"Pass",IF($J$103&lt;'Settings'!$B$4,"Thin",IF($J$103&lt;0.06,"✅ Sharp band",IF($J$103&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.0% (fair -104). Your call.</t>
+        </is>
+      </c>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="16">
+        <f>IF(OR($H$103="",$O$103=""),"",(1+IF($H$103&lt;0,-100/$H$103,$H$103/100))/(1+IF($O$103&lt;0,-100/$O$103,$O$103/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Under 7.5</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I104" s="13">
+        <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="16">
+        <f>IF($H$104="","",$F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF($H$104="","",MAX(0,($F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))/IF($H$104&lt;0,-100/$H$104,$H$104/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L104" s="18">
+        <f>IF($H$104="","",ROUND(MIN($K$104,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M104" s="12">
+        <f>IF($J$104="","",IF($J$104&lt;0,"Pass",IF($J$104&lt;'Settings'!$B$4,"Thin",IF($J$104&lt;0.06,"✅ Sharp band",IF($J$104&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.0% (fair +104). Your call.</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="16">
+        <f>IF(OR($H$104="",$O$104=""),"",(1+IF($H$104&lt;0,-100/$H$104,$H$104/100))/(1+IF($O$104&lt;0,-100/$O$104,$O$104/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets -1.5</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>162</v>
+      </c>
+      <c r="I105" s="13">
+        <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>IF($H$105="","",$F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF($H$105="","",MAX(0,($F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))/IF($H$105&lt;0,-100/$H$105,$H$105/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>IF($H$105="","",ROUND(MIN($K$105,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M105" s="12">
+        <f>IF($J$105="","",IF($J$105&lt;0,"Pass",IF($J$105&lt;'Settings'!$B$4,"Thin",IF($J$105&lt;0.06,"✅ Sharp band",IF($J$105&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.5% (fair +166). Your call.</t>
+        </is>
+      </c>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="16">
+        <f>IF(OR($H$105="",$O$105=""),"",(1+IF($H$105&lt;0,-100/$H$105,$H$105/100))/(1+IF($O$105&lt;0,-100/$O$105,$O$105/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox +1.5</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>-166</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I106" s="13">
+        <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="16">
+        <f>IF($H$106="","",$F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF($H$106="","",MAX(0,($F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))/IF($H$106&lt;0,-100/$H$106,$H$106/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>IF($H$106="","",ROUND(MIN($K$106,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M106" s="12">
+        <f>IF($J$106="","",IF($J$106&lt;0,"Pass",IF($J$106&lt;'Settings'!$B$4,"Thin",IF($J$106&lt;0.06,"✅ Sharp band",IF($J$106&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.5% (fair -166). Your call.</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="16">
+        <f>IF(OR($H$106="",$O$106=""),"",(1+IF($H$106&lt;0,-100/$H$106,$H$106/100))/(1+IF($O$106&lt;0,-100/$O$106,$O$106/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.4256172</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>138</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.6% (fair +135). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.5743828</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>-135</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.4% (fair -135). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Over 7.5</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>-131</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.8% (fair -131). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Under 7.5</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.2% (fair +131). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox +1.5</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.6472</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>-183</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.7% (fair -183). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Athletics -1.5</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>183</v>
+      </c>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.3% (fair +183). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.5105999999999999</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.1% (fair -104). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.4894</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.9% (fair +104). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H115" s="15" t="n"/>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.2% (fair +121). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H116" s="15" t="n"/>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.8% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H117" s="15" t="n"/>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.8% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H118" s="15" t="n"/>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.2% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.2% (fair +126). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.8% (fair -126). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals +1.5</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I121" s="13">
+        <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
+        <v/>
+      </c>
+      <c r="J121" s="16">
+        <f>IF($H$121="","",$F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF($H$121="","",MAX(0,($F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))/IF($H$121&lt;0,-100/$H$121,$H$121/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L121" s="18">
+        <f>IF($H$121="","",ROUND(MIN($K$121,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M121" s="12">
+        <f>IF($J$121="","",IF($J$121&lt;0,"Pass",IF($J$121&lt;'Settings'!$B$4,"Thin",IF($J$121&lt;0.06,"✅ Sharp band",IF($J$121&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N121" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.2% (fair -128). Your call.</t>
+        </is>
+      </c>
+      <c r="O121" s="15" t="n"/>
+      <c r="P121" s="16">
+        <f>IF(OR($H$121="",$O$121=""),"",(1+IF($H$121&lt;0,-100/$H$121,$H$121/100))/(1+IF($O$121&lt;0,-100/$O$121,$O$121/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves -1.5</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0.4379999999999999</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="I122" s="13">
+        <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
+        <v/>
+      </c>
+      <c r="J122" s="16">
+        <f>IF($H$122="","",$F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))</f>
+        <v/>
+      </c>
+      <c r="K122" s="17">
+        <f>IF($H$122="","",MAX(0,($F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))/IF($H$122&lt;0,-100/$H$122,$H$122/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L122" s="18">
+        <f>IF($H$122="","",ROUND(MIN($K$122,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M122" s="12">
+        <f>IF($J$122="","",IF($J$122&lt;0,"Pass",IF($J$122&lt;'Settings'!$B$4,"Thin",IF($J$122&lt;0.06,"✅ Sharp band",IF($J$122&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N122" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.8% (fair +128). Your call.</t>
+        </is>
+      </c>
+      <c r="O122" s="15" t="n"/>
+      <c r="P122" s="16">
+        <f>IF(OR($H$122="",$O$122=""),"",(1+IF($H$122&lt;0,-100/$H$122,$H$122/100))/(1+IF($O$122&lt;0,-100/$O$122,$O$122/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H123" s="15" t="n"/>
+      <c r="I123" s="13">
+        <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
+        <v/>
+      </c>
+      <c r="J123" s="16">
+        <f>IF($H$123="","",$F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))</f>
+        <v/>
+      </c>
+      <c r="K123" s="17">
+        <f>IF($H$123="","",MAX(0,($F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))/IF($H$123&lt;0,-100/$H$123,$H$123/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L123" s="18">
+        <f>IF($H$123="","",ROUND(MIN($K$123,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M123" s="12">
+        <f>IF($J$123="","",IF($J$123&lt;0,"Pass",IF($J$123&lt;'Settings'!$B$4,"Thin",IF($J$123&lt;0.06,"✅ Sharp band",IF($J$123&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N123" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.1% (fair +108). Your call.</t>
+        </is>
+      </c>
+      <c r="O123" s="15" t="n"/>
+      <c r="P123" s="16">
+        <f>IF(OR($H$123="",$O$123=""),"",(1+IF($H$123&lt;0,-100/$H$123,$H$123/100))/(1+IF($O$123&lt;0,-100/$O$123,$O$123/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H124" s="15" t="n"/>
+      <c r="I124" s="13">
+        <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
+        <v/>
+      </c>
+      <c r="J124" s="16">
+        <f>IF($H$124="","",$F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))</f>
+        <v/>
+      </c>
+      <c r="K124" s="17">
+        <f>IF($H$124="","",MAX(0,($F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))/IF($H$124&lt;0,-100/$H$124,$H$124/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L124" s="18">
+        <f>IF($H$124="","",ROUND(MIN($K$124,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M124" s="12">
+        <f>IF($J$124="","",IF($J$124&lt;0,"Pass",IF($J$124&lt;'Settings'!$B$4,"Thin",IF($J$124&lt;0.06,"✅ Sharp band",IF($J$124&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N124" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.8% (fair -108). Your call.</t>
+        </is>
+      </c>
+      <c r="O124" s="15" t="n"/>
+      <c r="P124" s="16">
+        <f>IF(OR($H$124="",$O$124=""),"",(1+IF($H$124&lt;0,-100/$H$124,$H$124/100))/(1+IF($O$124&lt;0,-100/$O$124,$O$124/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>187</v>
+      </c>
+      <c r="H125" s="15" t="n"/>
+      <c r="I125" s="13">
+        <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
+        <v/>
+      </c>
+      <c r="J125" s="16">
+        <f>IF($H$125="","",$F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))</f>
+        <v/>
+      </c>
+      <c r="K125" s="17">
+        <f>IF($H$125="","",MAX(0,($F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))/IF($H$125&lt;0,-100/$H$125,$H$125/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L125" s="18">
+        <f>IF($H$125="","",ROUND(MIN($K$125,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M125" s="12">
+        <f>IF($J$125="","",IF($J$125&lt;0,"Pass",IF($J$125&lt;'Settings'!$B$4,"Thin",IF($J$125&lt;0.06,"✅ Sharp band",IF($J$125&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N125" s="19" t="inlineStr">
+        <is>
+          <t>Model 34.9% (fair +187). Your call.</t>
+        </is>
+      </c>
+      <c r="O125" s="15" t="n"/>
+      <c r="P125" s="16">
+        <f>IF(OR($H$125="",$O$125=""),"",(1+IF($H$125&lt;0,-100/$H$125,$H$125/100))/(1+IF($O$125&lt;0,-100/$O$125,$O$125/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>-187</v>
+      </c>
+      <c r="H126" s="15" t="n"/>
+      <c r="I126" s="13">
+        <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
+        <v/>
+      </c>
+      <c r="J126" s="16">
+        <f>IF($H$126="","",$F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))</f>
+        <v/>
+      </c>
+      <c r="K126" s="17">
+        <f>IF($H$126="","",MAX(0,($F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))/IF($H$126&lt;0,-100/$H$126,$H$126/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L126" s="18">
+        <f>IF($H$126="","",ROUND(MIN($K$126,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M126" s="12">
+        <f>IF($J$126="","",IF($J$126&lt;0,"Pass",IF($J$126&lt;'Settings'!$B$4,"Thin",IF($J$126&lt;0.06,"✅ Sharp band",IF($J$126&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N126" s="19" t="inlineStr">
+        <is>
+          <t>Model 65.1% (fair -187). Your call.</t>
+        </is>
+      </c>
+      <c r="O126" s="15" t="n"/>
+      <c r="P126" s="16">
+        <f>IF(OR($H$126="",$O$126=""),"",(1+IF($H$126&lt;0,-100/$H$126,$H$126/100))/(1+IF($O$126&lt;0,-100/$O$126,$O$126/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="H127" s="15" t="n"/>
+      <c r="I127" s="13">
+        <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>IF($H$127="","",$F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))</f>
+        <v/>
+      </c>
+      <c r="K127" s="17">
+        <f>IF($H$127="","",MAX(0,($F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))/IF($H$127&lt;0,-100/$H$127,$H$127/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L127" s="18">
+        <f>IF($H$127="","",ROUND(MIN($K$127,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M127" s="12">
+        <f>IF($J$127="","",IF($J$127&lt;0,"Pass",IF($J$127&lt;'Settings'!$B$4,"Thin",IF($J$127&lt;0.06,"✅ Sharp band",IF($J$127&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N127" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.1% (fair +117). Your call.</t>
+        </is>
+      </c>
+      <c r="O127" s="15" t="n"/>
+      <c r="P127" s="16">
+        <f>IF(OR($H$127="",$O$127=""),"",(1+IF($H$127&lt;0,-100/$H$127,$H$127/100))/(1+IF($O$127&lt;0,-100/$O$127,$O$127/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="G128" s="14" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="13">
+        <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
+        <v/>
+      </c>
+      <c r="J128" s="16">
+        <f>IF($H$128="","",$F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))</f>
+        <v/>
+      </c>
+      <c r="K128" s="17">
+        <f>IF($H$128="","",MAX(0,($F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))/IF($H$128&lt;0,-100/$H$128,$H$128/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L128" s="18">
+        <f>IF($H$128="","",ROUND(MIN($K$128,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M128" s="12">
+        <f>IF($J$128="","",IF($J$128&lt;0,"Pass",IF($J$128&lt;'Settings'!$B$4,"Thin",IF($J$128&lt;0.06,"✅ Sharp band",IF($J$128&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N128" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.9% (fair -117). Your call.</t>
+        </is>
+      </c>
+      <c r="O128" s="15" t="n"/>
+      <c r="P128" s="16">
+        <f>IF(OR($H$128="",$O$128=""),"",(1+IF($H$128&lt;0,-100/$H$128,$H$128/100))/(1+IF($O$128&lt;0,-100/$O$128,$O$128/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J100">
+  <conditionalFormatting sqref="J5:J128">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -17072,13 +18918,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2145</v>
+        <v>0.2114</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -17102,7 +18948,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 21.5% (fair +366). Your call.</t>
+          <t>Model 21.1% (fair +373). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -17138,13 +18984,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7855</v>
+        <v>0.7886</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-366</v>
+        <v>-373</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-426</v>
+        <v>-456</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -17168,7 +19014,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 78.5% (fair -366). Your call.</t>
+          <t>Model 78.9% (fair -373). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -17204,13 +19050,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5333</v>
+        <v>0.537</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-114</v>
+        <v>-116</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -17234,7 +19080,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -17270,13 +19116,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.463</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -17300,7 +19146,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -17332,17 +19178,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -11.5</t>
+          <t>Atlanta Dream -12.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4121385528638312</v>
+        <v>0.3817883079419142</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -17366,7 +19212,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -17398,14 +19244,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +11.5</t>
+          <t>Seattle Storm +12.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5878614471361688</v>
+        <v>0.6182116920580858</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-143</v>
+        <v>-162</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>376</v>
@@ -17432,7 +19278,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -17468,13 +19314,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6424395000000001</v>
+        <v>0.5639000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-180</v>
+        <v>-129</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17498,7 +19344,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -180). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -17534,10 +19380,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3575605</v>
+        <v>0.4361</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-104</v>
@@ -17564,7 +19410,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +180). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -17596,17 +19442,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 172</t>
+          <t>Over 171.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6532529086000657</v>
+        <v>0.582</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-188</v>
+        <v>-139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -17630,7 +19476,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -17662,17 +19508,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 172</t>
+          <t>Under 171.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3250470913999343</v>
+        <v>0.418</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -17696,7 +19542,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +208). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -17864,13 +19710,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7572</v>
+        <v>0.7545999999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-312</v>
+        <v>-307</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-345</v>
+        <v>-335</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17894,7 +19740,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 75.7% (fair -312). Your call.</t>
+          <t>Model 75.5% (fair -307). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17930,13 +19776,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2428</v>
+        <v>0.2454</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17960,7 +19806,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 24.3% (fair +312). Your call.</t>
+          <t>Model 24.5% (fair +307). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17992,17 +19838,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 174.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.5797197054418918</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-120</v>
+        <v>-138</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -18026,7 +19872,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -18058,14 +19904,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 174.5</t>
+          <t>Under 175.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.4202802945581082</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-104</v>
@@ -18092,7 +19938,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -18200,7 +20046,7 @@
         <v>122</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -18260,13 +20106,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.7643</v>
+        <v>0.74107</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-324</v>
+        <v>-286</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-355</v>
+        <v>-285</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -18290,7 +20136,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 76.4% (fair -324). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -18326,13 +20172,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.2357</v>
+        <v>0.25893</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -18356,7 +20202,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 23.6% (fair +324). Your call.</t>
+          <t>Model 25.9% (fair +286). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -18392,13 +20238,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6534700194739194</v>
+        <v>0.5816</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-189</v>
+        <v>-139</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>111</v>
+        <v>-104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -18422,7 +20268,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -189). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -18458,10 +20304,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3465299805260806</v>
+        <v>0.4184</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>104</v>
@@ -18488,7 +20334,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +189). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -18520,17 +20366,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun +8.5</t>
+          <t>Connecticut Sun +6.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.537</v>
+        <v>0.4814731254206738</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-116</v>
+        <v>108</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -18554,7 +20400,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -18586,17 +20432,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -8.5</t>
+          <t>Golden State Valkyries -6.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.463</v>
+        <v>0.5185268745793262</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -18620,7 +20466,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -18788,13 +20634,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5326</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -18818,7 +20664,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -18854,10 +20700,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4651</v>
+        <v>0.4674</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>100</v>
@@ -18884,7 +20730,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -19052,13 +20898,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4471000000000001</v>
+        <v>0.4459</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>124</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -19082,7 +20928,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -19118,7 +20964,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5541</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-124</v>
@@ -19148,7 +20994,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -19184,13 +21030,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.5422</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>-118</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -19214,7 +21060,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -19250,13 +21096,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4597</v>
+        <v>0.4578</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>118</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -19280,7 +21126,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -19316,13 +21162,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5209</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-111</v>
+        <v>-109</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -19346,7 +21192,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -19382,10 +21228,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.4791</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-104</v>
@@ -19412,7 +21258,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>

--- a/data/output/workbook/2026-07-09.xlsx
+++ b/data/output/workbook/2026-07-09.xlsx
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10925175"/>
+    <ext cx="10125075" cy="10753725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09 14:59</t>
+          <t>2026-07-09 15:58</t>
         </is>
       </c>
     </row>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6347</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-174</v>
+        <v>-176</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>170</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8949,32 +8949,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.7412000000000001</v>
+        <v>0.5644</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-286</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-153</v>
+        <v>120</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 74.1% (fair -286). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9015,32 +9015,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5361</v>
+        <v>0.2065</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-116</v>
+        <v>384</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>127</v>
+        <v>495</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 20.7% (fair +384). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,32 +9081,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.7412000000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-124</v>
+        <v>-286</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>120</v>
+        <v>-153</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.582</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>104</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Indiana Fever @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2114</v>
+        <v>0.5663</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>373</v>
+        <v>-131</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>456</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 21.1% (fair +373). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9274,37 +9274,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Phoenix Mercury</t>
+          <t>Golden State Valkyries @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Over 154.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5639000000000001</v>
+        <v>0.5767</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-129</v>
+        <v>-136</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries @ Connecticut Sun</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 154.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5575</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-139</v>
+        <v>-126</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>105</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9406,37 +9406,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4796</v>
+        <v>0.5288</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>109</v>
+        <v>-112</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9472,37 +9472,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5288</v>
+        <v>0.4771</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-112</v>
+        <v>110</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9543,32 +9543,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo +6.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.5616</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-118</v>
+        <v>-128</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5598000000000001</v>
+        <v>0.5604</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-127</v>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Las Vegas Aces @ Portland Fire</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 174.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5476</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9736,17 +9736,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9756,17 +9756,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5575</v>
+        <v>0.542</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-126</v>
+        <v>-118</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9802,37 +9802,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5541</v>
+        <v>0.5182</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-124</v>
+        <v>-108</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Dallas Wings @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4894</v>
+        <v>0.2999</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>122</v>
+        <v>264</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 30.0% (fair +233). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 180.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.4894</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-118</v>
+        <v>104</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3018</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>231</v>
+        <v>-124</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>257</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,32 +10071,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Dallas Wings @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Toronto Tempo +6.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5057</v>
+        <v>0.5522</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-102</v>
+        <v>-123</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10203,32 +10203,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.537</v>
+        <v>0.4764</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-116</v>
+        <v>110</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10264,37 +10264,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4754</v>
+        <v>0.5151</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>110</v>
+        <v>-106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,32 +10335,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5286</v>
+        <v>0.4818</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-112</v>
+        <v>108</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10396,17 +10396,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 168.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5119</v>
+        <v>0.5395</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-105</v>
+        <v>-117</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4353</v>
+        <v>0.4343</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>130</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5657</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-130</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4566</v>
+        <v>0.458</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>113</v>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.542</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>106</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,10 +11287,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3908</v>
+        <v>0.3921</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>153</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6092</v>
+        <v>0.6079</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-156</v>
+        <v>-155</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-156</v>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4576</v>
+        <v>0.4566</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>119</v>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +119). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5424</v>
+        <v>0.5434</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-119</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4522</v>
+        <v>0.4512</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>102</v>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4658</v>
+        <v>0.4667999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>106</v>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,7 +12079,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3652</v>
+        <v>0.3653</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>174</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6348</v>
+        <v>0.6347</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-174</v>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4831</v>
+        <v>0.4832</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>107</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5169</v>
+        <v>0.5168</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-107</v>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4472</v>
+        <v>0.4356</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>117</v>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.5644</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-124</v>
+        <v>-130</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>120</v>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3653</v>
+        <v>0.3624</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>170</v>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6347</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-174</v>
+        <v>-176</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>170</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4477</v>
+        <v>0.4586</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>117</v>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5523</v>
+        <v>0.5414</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-123</v>
+        <v>-118</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>-117</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5361</v>
+        <v>0.4818</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-116</v>
+        <v>108</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,13 +13201,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4639</v>
+        <v>0.5182</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,13 +13267,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3838</v>
+        <v>0.3682</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,13 +13333,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6162000000000001</v>
+        <v>0.6317999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-161</v>
+        <v>-172</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13399,13 +13399,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5038</v>
+        <v>0.5065999999999999</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13465,13 +13465,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4962</v>
+        <v>0.4934</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13537,7 +13537,7 @@
         <v>-112</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13603,7 +13603,7 @@
         <v>112</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13927,13 +13927,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4283</v>
+        <v>0.4159</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4897</v>
+        <v>0.5025000000000001</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>104</v>
+        <v>-101</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>-113</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4714</v>
+        <v>0.4757</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>-104</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5286</v>
+        <v>0.5243</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>102</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5246</v>
+        <v>0.5236000000000001</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-110</v>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4754</v>
+        <v>0.4764</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>110</v>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4901</v>
+        <v>0.4931</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>104</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5099</v>
+        <v>0.5069</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>-101</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,7 +14455,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5808</v>
+        <v>0.5819</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>-139</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4192</v>
+        <v>0.4181</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>139</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -15235,13 +15235,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5204</v>
+        <v>0.5228999999999999</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -109). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15301,10 +15301,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4796</v>
+        <v>0.4771</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>136</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15763,10 +15763,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4643</v>
+        <v>0.4384</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>113</v>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15829,13 +15829,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5357000000000001</v>
+        <v>0.5616</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-115</v>
+        <v>-128</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5057</v>
+        <v>0.5567800000000001</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-102</v>
+        <v>-126</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>113</v>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16093,13 +16093,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4943</v>
+        <v>0.44322</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16159,10 +16159,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5119</v>
+        <v>0.5151</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>108</v>
@@ -16189,7 +16189,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16225,13 +16225,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4881</v>
+        <v>0.4849</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16423,13 +16423,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.474</v>
+        <v>0.4802999999999999</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16489,13 +16489,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.526</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4875</v>
+        <v>0.4841</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16585,7 +16585,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16621,10 +16621,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5125</v>
+        <v>0.5159</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>100</v>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16687,13 +16687,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.6283</v>
+        <v>0.6269</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-169</v>
+        <v>-168</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-188</v>
+        <v>-185</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.3717</v>
+        <v>0.3731</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>155</v>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4492</v>
+        <v>0.4443</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>117</v>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17017,13 +17017,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5508</v>
+        <v>0.5557</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-123</v>
+        <v>-125</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17083,10 +17083,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.51</v>
+        <v>0.5208</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-104</v>
+        <v>-109</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>-115</v>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17149,10 +17149,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.49</v>
+        <v>0.4792</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>108</v>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17215,10 +17215,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3755</v>
+        <v>0.3779</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>162</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-166</v>
+        <v>-165</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>-170</v>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17347,10 +17347,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4256172</v>
+        <v>0.4238366</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>138</v>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17413,10 +17413,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5743828</v>
+        <v>0.5761634</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>117</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5676</v>
+        <v>0.5699</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-131</v>
+        <v>-133</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>-115</v>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17545,10 +17545,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4324</v>
+        <v>0.4301</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>108</v>
@@ -17575,7 +17575,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.6472</v>
+        <v>0.6441</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-183</v>
+        <v>-181</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>-170</v>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 64.7% (fair -183). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17677,10 +17677,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.3528</v>
+        <v>0.3559</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="13">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 35.3% (fair +183). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -18201,7 +18201,7 @@
         <v>-126</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3488</v>
+        <v>0.3601</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H125" s="15" t="n"/>
       <c r="I125" s="13">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +187). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18585,10 +18585,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6512</v>
+        <v>0.6399</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-187</v>
+        <v>-178</v>
       </c>
       <c r="H126" s="15" t="n"/>
       <c r="I126" s="13">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -187). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18649,10 +18649,10 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.4688</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H127" s="15" t="n"/>
       <c r="I127" s="13">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18713,10 +18713,10 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5389</v>
+        <v>0.5312</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="H128" s="15" t="n"/>
       <c r="I128" s="13">
@@ -18741,7 +18741,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18918,13 +18918,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2114</v>
+        <v>0.2065</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 21.1% (fair +373). Your call.</t>
+          <t>Model 20.7% (fair +384). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -18984,10 +18984,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7886</v>
+        <v>0.7935</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-373</v>
+        <v>-384</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-456</v>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 78.9% (fair -373). Your call.</t>
+          <t>Model 79.3% (fair -384). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19050,13 +19050,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.537</v>
+        <v>0.5395</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.463</v>
+        <v>0.4605</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19314,13 +19314,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5639000000000001</v>
+        <v>0.5663</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-129</v>
+        <v>-131</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4361</v>
+        <v>0.4337</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-104</v>
@@ -19410,7 +19410,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19446,10 +19446,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.582</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>104</v>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -19512,13 +19512,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.418</v>
+        <v>0.4229000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -19578,13 +19578,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4402</v>
+        <v>0.4396</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>127</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5598000000000001</v>
+        <v>0.5604</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-127</v>
@@ -19710,10 +19710,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7545999999999999</v>
+        <v>0.7556</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-307</v>
+        <v>-309</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-335</v>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 75.5% (fair -307). Your call.</t>
+          <t>Model 75.6% (fair -309). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -19776,13 +19776,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2454</v>
+        <v>0.2444</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -19806,7 +19806,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 24.5% (fair +307). Your call.</t>
+          <t>Model 24.4% (fair +309). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -19838,17 +19838,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 175.5</t>
+          <t>Over 174.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5797197054418918</v>
+        <v>0.5476</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-138</v>
+        <v>-121</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -19904,17 +19904,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 175.5</t>
+          <t>Under 174.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4202802945581082</v>
+        <v>0.4524</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -20046,7 +20046,7 @@
         <v>122</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -20106,13 +20106,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.74107</v>
+        <v>0.7494000000000001</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-286</v>
+        <v>-299</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-285</v>
+        <v>-292</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 74.1% (fair -286). Your call.</t>
+          <t>Model 74.9% (fair -299). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.25893</v>
+        <v>0.2506</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 25.9% (fair +286). Your call.</t>
+          <t>Model 25.1% (fair +299). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -20238,13 +20238,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5767</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -20268,7 +20268,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4184</v>
+        <v>0.4233</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6981999999999999</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-231</v>
+        <v>-233</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>-257</v>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 69.8% (fair -231). Your call.</t>
+          <t>Model 70.0% (fair -233). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -20568,13 +20568,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.3018</v>
+        <v>0.2999</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 30.0% (fair +233). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -20634,13 +20634,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5326</v>
+        <v>0.5349</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4674</v>
+        <v>0.4651</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>100</v>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -20766,13 +20766,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.5522</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-118</v>
+        <v>-123</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -20832,13 +20832,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4585</v>
+        <v>0.4478</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -20862,7 +20862,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -20898,13 +20898,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4459</v>
+        <v>0.4471000000000001</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>124</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -20964,7 +20964,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5541</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-124</v>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -21026,17 +21026,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 180.5</t>
+          <t>Over 180</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -21092,14 +21092,14 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 180.5</t>
+          <t>Under 180</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4578</v>
+        <v>0.4292</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>104</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -21373,22 +21373,22 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2504</v>
+        <v>0.2503</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4191</v>
+        <v>0.4181</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-35.25</v>
+        <v>-36.25</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>5.36</v>
@@ -21404,22 +21404,22 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2502</v>
+        <v>0.2501</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4231</v>
+        <v>0.4219</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-31.77</v>
+        <v>-32.77</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-8.73</v>
+        <v>-8.98</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>7.01</v>
@@ -21508,7 +21508,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=356, ECE 0.056 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=357, ECE 0.057 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21622,16 +21622,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.543</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5486</v>
+        <v>0.5517</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>0.0056</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -22771,7 +22771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22788,171 +22788,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs New York Mets defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.349</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.349</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.1</v>
+        <v>7.792</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.871</v>
+        <v>7.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -23016,22 +23095,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.918</v>
+        <v>0.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -23095,321 +23174,321 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.918</v>
+        <v>9.061</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.537</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.7</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.061</v>
+        <v>0.519</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Kansas City Royals defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.967</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.059</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>6.533</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.967</v>
+        <v>7.306</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.265</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.306</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -23473,22 +23552,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -23552,151 +23631,72 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.556</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.208</v>
+        <v>0.838</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
